--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Desktop\Facultate_anul_3\Semestrul2\VVSS\Laborator\MyDrinkShop\docs\Lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emato\IdeaProjects\VVSSLabs\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C294F6D-DDEF-4858-A403-FE762A5FC6A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D6A721-8D7E-4A82-B889-5723B2118D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="113">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -255,13 +255,153 @@
   </si>
   <si>
     <t>src/main/java/drinkshop/service/OrderService.java</t>
+  </si>
+  <si>
+    <t>pom.xml</t>
+  </si>
+  <si>
+    <t>javafx-controls is duplicated, with different versions (21 and 22.0.1)</t>
+  </si>
+  <si>
+    <t>src/main/java/drinkshop/service/StocService.java</t>
+  </si>
+  <si>
+    <t>Whilst calculating the value of variable "deScazut",  which is a double variable, the source code casts it to int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The import of java.util.Map is not used </t>
+  </si>
+  <si>
+    <t>src/main/java/drinkshop/service/validator/RetetaValidator.java</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AtomicReference&lt;String&gt; is used out of purpose, there is no concurrent context </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Possible NullPointerException: of variable "ingrediente" is null, the code enters the stream() and throws and error </t>
+  </si>
+  <si>
+    <t>src/main/java/drinkshop/reports/DailyReportService.java</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imports of List, Collectors, and StreamSupport are unused </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The standard requires use of !isEmpthy() instead of size()&gt; </t>
+  </si>
+  <si>
+    <t>src/test/java/drinkshop/domain/ProductTest.java</t>
+  </si>
+  <si>
+    <t>The standard requires the use of assertEquals and assertNotNull</t>
+  </si>
+  <si>
+    <t>Emanuela-Coralia Toda-Puiulet</t>
+  </si>
+  <si>
+    <t>src/main/java/drinkshop/repository/AbstractRepository.java</t>
+  </si>
+  <si>
+    <t>update() is identical to save()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @Override
+    public E save(E entity) {
+        entities.put(getId(entity), entity);
+        return entity;
+    }
+    @Override
+    public E delete(ID id) {
+        return entities.remove(id);
+    }
+    @Override
+    public E update(E entity) {
+        entities.put(getId(entity), entity);
+        return entity;
+    }</t>
+  </si>
+  <si>
+    <t>update() should verify the entity exists first. If it doesn't, it should signal that (return null, throw, etc.). Having two methods with identical bodies is misleading and violates the principle of least surprise. A defensive check makes the contract clear: save creates, update modifies.</t>
+  </si>
+  <si>
+    <t>&lt;ID, E&gt; — ID is two uppercase letters, which violates the convention.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Java convention (and Sonar rule java:S119) expects single-letter type parameters optionally followed by a digit. Multi-letter names like ID look like class names and reduce readability in generic contexts
+</t>
+  </si>
+  <si>
+    <t>Generic type p
+arameter names don't match ^[A-Z][0-9]?$</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unnecessary cast to List in findAll()
+</t>
+  </si>
+  <si>
+    <t>return (List&lt;E&gt;) entities.values();</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> return StreamSupport.stream(entities.values().spliterator(), false).toList();
+</t>
+  </si>
+  <si>
+    <t>Commented-out code block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">//                    .collect(Collectors.toList());
+// return (List&lt;E&gt;) entities.values();
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead/commented-out code is technical debt — it confuses future readers about intent, clutters diffs, and is better preserved in version control history if needed.
+</t>
+  </si>
+  <si>
+    <t>src/main/java/drinkshop/repository/file/FileAbstractRepository.java</t>
+  </si>
+  <si>
+    <t>Constructor visibility should be protected</t>
+  </si>
+  <si>
+    <t>public FileAbstractRepository(String fileName)</t>
+  </si>
+  <si>
+    <t>This is an abstract class — it can't be instantiated directly. A public constructor is misleading since only subclasses call it. Making it protected accurately reflects its intended usage.</t>
+  </si>
+  <si>
+    <t>Generic name ID doesn't match ^[A-Z][0-9]?$</t>
+  </si>
+  <si>
+    <t>&lt;ID, E&gt;</t>
+  </si>
+  <si>
+    <t>ID → K to match convention and stay consistent with the fixed AbstractRepository&lt;K, E&gt;</t>
+  </si>
+  <si>
+    <t>Commented-out code</t>
+  </si>
+  <si>
+    <t>//loadFromFile()</t>
+  </si>
+  <si>
+    <t>Dead/commented-out code is technical debt — it confuses future readers about intent, clutters diffs, and is better preserved in version control history if needed.</t>
+  </si>
+  <si>
+    <t>C012</t>
+  </si>
+  <si>
+    <t>C05</t>
+  </si>
+  <si>
+    <t>C04</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -359,6 +499,30 @@
       <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFBCBEC4"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFB3AE60"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFCF8E6D"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="5">
@@ -460,7 +624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -492,17 +656,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -510,17 +683,30 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -830,7 +1016,7 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="6"/>
     <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
@@ -843,18 +1029,18 @@
     <col min="11" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.6">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="B2" s="26" t="s">
         <v>16</v>
       </c>
@@ -869,7 +1055,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
@@ -880,7 +1066,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
@@ -898,40 +1084,40 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="28"/>
+      <c r="E5" s="31"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="23"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E6" s="28"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="23"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E7" s="28"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -945,7 +1131,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="72">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -959,7 +1145,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="43.2">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -974,7 +1160,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="43.2">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
@@ -989,7 +1175,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="57.6">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1004,7 +1190,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="28.8">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1019,7 +1205,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="43.2">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1034,7 +1220,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="43.2">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1049,7 +1235,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1058,7 +1244,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1067,7 +1253,7 @@
       <c r="D18" s="3"/>
       <c r="E18" s="15"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1076,7 +1262,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="15"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1085,7 +1271,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="15"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1094,7 +1280,7 @@
       <c r="D21" s="3"/>
       <c r="E21" s="15"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1103,7 +1289,7 @@
       <c r="D22" s="3"/>
       <c r="E22" s="15"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1112,7 +1298,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="15"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1121,7 +1307,7 @@
       <c r="D24" s="3"/>
       <c r="E24" s="15"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1130,7 +1316,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="15"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5">
       <c r="C27" s="11" t="s">
         <v>8</v>
       </c>
@@ -1160,7 +1346,7 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="6"/>
     <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
@@ -1172,18 +1358,18 @@
     <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.6">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="B2" s="26" t="s">
         <v>15</v>
       </c>
@@ -1198,7 +1384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
@@ -1209,14 +1395,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="30"/>
+      <c r="E4" s="32"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -1227,40 +1413,40 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="28"/>
+      <c r="E5" s="31"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="23"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E6" s="28"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="23"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E7" s="28"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1274,7 +1460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="43.2">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -1288,7 +1474,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="43.2">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -1303,7 +1489,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="57.6">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
@@ -1318,7 +1504,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="43.2">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1333,7 +1519,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="57.6">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1348,7 +1534,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1357,7 +1543,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1366,7 +1552,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1375,7 +1561,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1384,7 +1570,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1393,7 +1579,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1402,7 +1588,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1411,7 +1597,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1420,7 +1606,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1429,7 +1615,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1438,7 +1624,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1447,7 +1633,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1456,7 +1642,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5">
       <c r="C28" s="11" t="s">
         <v>8</v>
       </c>
@@ -1486,7 +1672,7 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="6"/>
     <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
@@ -1498,18 +1684,18 @@
     <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.6">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="B2" s="26" t="s">
         <v>14</v>
       </c>
@@ -1524,7 +1710,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
@@ -1535,14 +1721,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="27"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -1553,40 +1739,40 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="28"/>
+      <c r="E5" s="31"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="23"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E6" s="28"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="23"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E7" s="28"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1600,7 +1786,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="86.4">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -1614,7 +1800,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="86.4">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -1629,7 +1815,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="72">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
@@ -1644,7 +1830,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="57.6">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1659,88 +1845,135 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="28.8">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="43.2">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="28.8">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C17" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="43.2">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="28.8">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="28.8">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="28.8">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C21" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="2:5">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1749,7 +1982,7 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1758,7 +1991,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1767,7 +2000,7 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1776,7 +2009,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1785,7 +2018,7 @@
       <c r="D27" s="2"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1794,7 +2027,7 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1803,7 +2036,7 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1812,7 +2045,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5">
       <c r="C32" s="11" t="s">
         <v>8</v>
       </c>
@@ -1841,31 +2074,31 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="6"/>
     <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
     <col min="3" max="3" width="16.21875" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="49" style="6" customWidth="1"/>
+    <col min="6" max="6" width="39.77734375" style="6" customWidth="1"/>
     <col min="7" max="8" width="8.88671875" style="6"/>
     <col min="9" max="9" width="26.77734375" style="6" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.6">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="B2" s="26" t="s">
         <v>28</v>
       </c>
@@ -1880,7 +2113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
@@ -1891,12 +2124,12 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="C4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -1907,28 +2140,30 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
+      <c r="D5" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="28"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
       <c r="F6" s="20"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1945,166 +2180,222 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="243.6" customHeight="1">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="86.4">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="57.6">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="72">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="72">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="57.6">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="57.6">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="37"/>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="37"/>
+    </row>
+    <row r="19" spans="2:6">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="37"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="37"/>
+    </row>
+    <row r="21" spans="2:6">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="37"/>
+    </row>
+    <row r="22" spans="2:6">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="37"/>
+    </row>
+    <row r="23" spans="2:6">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="37"/>
+    </row>
+    <row r="24" spans="2:6">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="37"/>
+    </row>
+    <row r="25" spans="2:6">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+      <c r="E25" s="36"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2114,7 +2405,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2124,7 +2415,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2134,7 +2425,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2144,7 +2435,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2154,15 +2445,15 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C32" s="31" t="s">
+    <row r="32" spans="2:6">
+      <c r="C32" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
       <c r="F32" s="18"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="6:6">
       <c r="F35" s="21"/>
     </row>
   </sheetData>

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emato\IdeaProjects\VVSSLabs\docs\Lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Desktop\Facultate_anul_3\Semestrul2\VVSS\Laborator\MyDrinkShop\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D6A721-8D7E-4A82-B889-5723B2118D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47105AC-6F80-4D56-82B2-5723809BF5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="115">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -395,6 +395,12 @@
   </si>
   <si>
     <t>C04</t>
+  </si>
+  <si>
+    <t>Trifan Alexandra-Isabela, Emanuela-Coralia Toda-Puiulet</t>
+  </si>
+  <si>
+    <t>SonarQube</t>
   </si>
 </sst>
 </file>
@@ -624,7 +630,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -656,36 +662,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -698,15 +674,44 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1034,19 +1039,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -1070,10 +1075,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="29"/>
+      <c r="E4" s="36"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -1088,10 +1093,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="35"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
@@ -1103,19 +1108,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="28"/>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="28"/>
+      <c r="E7" s="30"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -1363,19 +1368,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -1399,10 +1404,10 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="32"/>
+      <c r="E4" s="37"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -1417,10 +1422,10 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="35"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
@@ -1432,19 +1437,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="28"/>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="28"/>
+      <c r="E7" s="30"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -1689,19 +1694,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -1725,10 +1730,10 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="27"/>
+      <c r="E4" s="32"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -1743,10 +1748,10 @@
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="31"/>
+      <c r="D5" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="35"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
@@ -1758,19 +1763,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="28"/>
+      <c r="D6" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="28"/>
+      <c r="E7" s="30"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -1856,7 +1861,7 @@
       <c r="D14" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="40" t="s">
+      <c r="E14" s="29" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1901,7 +1906,7 @@
       <c r="D17" t="s">
         <v>78</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="29" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2092,19 +2097,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -2128,8 +2133,10 @@
       <c r="C4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
+      <c r="D4" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="32"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -2144,10 +2151,10 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="28"/>
+      <c r="E5" s="30"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
@@ -2159,8 +2166,10 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
+      <c r="D6" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="30"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10">
@@ -2190,7 +2199,7 @@
       <c r="D10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="E10" s="27" t="s">
         <v>89</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -2208,7 +2217,7 @@
       <c r="D11" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="27" t="s">
         <v>91</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -2226,7 +2235,7 @@
       <c r="D12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="27" t="s">
         <v>95</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -2244,7 +2253,7 @@
       <c r="D13" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="27" t="s">
         <v>98</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -2262,7 +2271,7 @@
       <c r="D14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -2280,7 +2289,7 @@
       <c r="D15" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="28" t="s">
         <v>105</v>
       </c>
       <c r="F15" s="2" t="s">
@@ -2298,7 +2307,7 @@
       <c r="D16" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="E16" s="27" t="s">
         <v>108</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -2310,80 +2319,80 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="37"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="1"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="37"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="1"/>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="37"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="1"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="37"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="1"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="37"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="1"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="37"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="1"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="37"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="1"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="37"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="1"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="3">
@@ -2392,7 +2401,7 @@
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="36"/>
+      <c r="E25" s="26"/>
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="2:6">
@@ -2446,12 +2455,14 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="18"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="18">
+        <v>2</v>
+      </c>
     </row>
     <row r="35" spans="6:6">
       <c r="F35" s="21"/>

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Desktop\Facultate_anul_3\Semestrul2\VVSS\Laborator\MyDrinkShop\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47105AC-6F80-4D56-82B2-5723809BF5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B1CE4C-5F0F-40B9-9996-9C7A9BE5CEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9324" yWindow="0" windowWidth="13812" windowHeight="13776" tabRatio="650" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -683,17 +683,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -701,17 +710,8 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1039,11 +1039,11 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10">
       <c r="B2" s="33" t="s">
@@ -1093,10 +1093,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="35"/>
+      <c r="E5" s="38"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
@@ -1108,19 +1108,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="30"/>
+      <c r="E6" s="35"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="30"/>
+      <c r="E7" s="35"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -1368,11 +1368,11 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10">
       <c r="B2" s="33" t="s">
@@ -1404,10 +1404,10 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="37"/>
+      <c r="E4" s="39"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -1422,10 +1422,10 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="35"/>
+      <c r="E5" s="38"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
@@ -1437,19 +1437,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="30"/>
+      <c r="E6" s="35"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="30"/>
+      <c r="E7" s="35"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -1682,7 +1682,7 @@
     <col min="1" max="1" width="8.88671875" style="6"/>
     <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
     <col min="3" max="3" width="16.21875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="25.88671875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="46.33203125" style="6" customWidth="1"/>
     <col min="5" max="5" width="41.44140625" style="6" customWidth="1"/>
     <col min="6" max="8" width="8.88671875" style="6"/>
     <col min="9" max="9" width="26.77734375" style="6" customWidth="1"/>
@@ -1694,11 +1694,11 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10">
       <c r="B2" s="33" t="s">
@@ -1730,10 +1730,10 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="32"/>
+      <c r="E4" s="34"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -1748,10 +1748,10 @@
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="35"/>
+      <c r="E5" s="38"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
@@ -1763,19 +1763,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="E6" s="30"/>
+      <c r="E6" s="35"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="30"/>
+      <c r="E7" s="35"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -2097,11 +2097,11 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10">
       <c r="B2" s="33" t="s">
@@ -2133,10 +2133,10 @@
       <c r="C4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="E4" s="32"/>
+      <c r="E4" s="34"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -2151,10 +2151,10 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="35"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
@@ -2166,10 +2166,10 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="30"/>
+      <c r="E6" s="35"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10">
@@ -2455,11 +2455,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
       <c r="F32" s="18">
         <v>2</v>
       </c>
